--- a/output/pdf_financials_xlsx/JSPX.xlsx
+++ b/output/pdf_financials_xlsx/JSPX.xlsx
@@ -5320,25 +5320,25 @@
         <v>5.076639</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>5.076639</v>
+        <v>0.736069</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.345822</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.718232</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.742777</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.084116</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.138128</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.151061</v>
       </c>
     </row>
     <row r="93">
@@ -8652,7 +8652,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10345,7 +10349,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -12883,7 +12891,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -15522,7 +15534,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -17528,7 +17544,11 @@
           <t>Reserves 16</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -20703,7 +20723,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/JSPX.xlsx
+++ b/output/pdf_financials_xlsx/JSPX.xlsx
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.188085</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.020593</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-5.671776</v>
+        <v>-5.859861</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-18.049276</v>
+        <v>-18.069869</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-5.493175</v>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-5.671776</v>
+        <v>-5.859861</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-18.049276</v>
+        <v>-18.069869</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-5.483327</v>
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.807785</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.643889</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.727748</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.517149</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.702932</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.487226</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.138856</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.060674</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>5.368041</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.117362</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.053204</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.534272</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.00743</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.017313</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.012553</v>
       </c>
     </row>
     <row r="35">
@@ -2274,49 +2274,49 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.807785</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.643889</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.727748</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.517149</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.702932</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.487226</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.138856</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.060674</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>5.368041</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.117362</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.053204</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.534272</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.00743</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.017313</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.012553</v>
       </c>
     </row>
     <row r="37">
@@ -2901,19 +2901,19 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.678162</v>
+        <v>0.034273</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.767927</v>
+        <v>0.040179</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.538787</v>
+        <v>0.021638</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.707295</v>
+        <v>0.004363</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.488476</v>
+        <v>0.00125</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
@@ -2922,25 +2922,25 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>5.484824</v>
+        <v>0.116783</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.128258</v>
+        <v>0.010896</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.077666</v>
+        <v>0.024462</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.580586</v>
+        <v>0.046314</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.00743</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.017313</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.012553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -22450,7 +22450,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -26434,7 +26434,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E209" s="5" t="n">
@@ -45905,7 +45905,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -47555,7 +47555,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -49187,7 +49187,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -50295,7 +50295,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -51217,7 +51217,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -63173,7 +63173,7 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E614" s="5" t="n">

--- a/output/pdf_financials_xlsx/JSPX.xlsx
+++ b/output/pdf_financials_xlsx/JSPX.xlsx
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-0.030749</v>
+        <v>0.016466</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-0.039311</v>
+        <v>0.169111</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0.053108</v>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0</v>
+        <v>0.8885</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>0</v>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.807785</v>
+        <v>0.887785</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1.643889</v>
+        <v>2.532389</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.727748</v>
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>0</v>
+        <v>2.093178</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>0</v>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.306541</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.161906</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>0</v>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0</v>
+        <v>2.399719</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>0.161906</v>
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.034273</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.040179</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>0</v>
+        <v>0.05647</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>0.8885</v>
@@ -5088,7 +5088,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>29.394367</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>32.365644</v>
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.441767</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>4.535658</v>
@@ -26525,7 +26525,11 @@
           <t>Interest and other receivables – Note 4</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>OtherReceivables</t>
+        </is>
+      </c>
       <c r="E210" s="5" t="n">
         <v>0.306541</v>
       </c>
@@ -26707,7 +26711,11 @@
           <t>Marketable securities – Note 3</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E212" s="5" t="n">
         <v>0.08</v>
       </c>
@@ -26796,7 +26804,11 @@
           <t>Loans receivable – Note 4</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>LoansReceivable</t>
+        </is>
+      </c>
       <c r="E213" s="5" t="n">
         <v>2.093178</v>
       </c>
@@ -26976,7 +26988,11 @@
           <t>Investments – Note 6</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E215" s="5" t="n">
         <v>0.05647</v>
       </c>
@@ -27065,7 +27081,11 @@
           <t>Restricted investments – Note 6</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>RestrictedInvestments</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -27516,7 +27536,11 @@
           <t>Share capital – Note 10</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E221" s="5" t="n">
         <v>29.394367</v>
       </c>
@@ -27605,7 +27629,11 @@
           <t>Contributed surplus – Note 10</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E222" s="5" t="n">
         <v>4.441767</v>
       </c>
@@ -62991,7 +63019,11 @@
           <t>Other income – Note 16</t>
         </is>
       </c>
-      <c r="D612" t="inlineStr"/>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E612" s="5" t="n">
         <v>0.047215</v>
       </c>
